--- a/results/LCA/lcia_results_per_kg_per_scenarios.xlsx
+++ b/results/LCA/lcia_results_per_kg_per_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_01741D0CE6EE8A7CA38EC8151565B5D7CDC122E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD5DF2B7-56FA-41C8-8358-7C64CB1580C0}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_01741D0CE6EE8A7CA38EC8151565B5D7CDC122E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCF20BD0-F13A-4D09-BA19-FA8B36992706}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ecosystem Quality" sheetId="1" r:id="rId1"/>
@@ -274,10 +274,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,9 +564,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -724,7 +724,7 @@
         <v>1.0796840951073009E-8</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -801,7 +801,7 @@
         <v>1.5037177448680371E-8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -878,7 +878,7 @@
         <v>1.706589238254627E-10</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -955,7 +955,7 @@
         <v>6.4150873934306188E-11</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>4.307186143247862E-8</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>2.76419553576033E-8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>5.6050315836556741E-10</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>7.6637922888438696E-10</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>5.3190367443890617E-8</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>2.0262478661578879E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>2.0511439781055759E-7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>2.2101440611200649E-7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>1.6317736341870269E-8</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>9.3398958840967376E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>1.3772535565051801E-7</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>2.0369722976204551E-7</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>1.541696770597969E-7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>2.1658530265339739E-7</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>1.9824109663449151E-8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>9.3398915281159411E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>1.0796840951073009E-8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>1.5037177448680371E-8</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>1.706589238254627E-10</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>6.4150873934306188E-11</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>4.307186143247862E-8</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>2.76419553576033E-8</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>5.6050315836556741E-10</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>7.6637922888438696E-10</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>5.3190367443890617E-8</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>2.0262478661578879E-7</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>2.0511439781055759E-7</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>2.2101440611200649E-7</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>1.6317736341870269E-8</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>9.3398958840967376E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>1.3772535565051801E-7</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>2.0369722976204551E-7</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>1.541696770597969E-7</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>2.1658530265339739E-7</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>1.9824109663449151E-8</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>9.3398915281159411E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>1.0796840951073009E-8</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>1.5037177448680371E-8</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>1.706589238254627E-10</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>6.4150873934306188E-11</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>4.307186143247862E-8</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>2.76419553576033E-8</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>5.6050315836556741E-10</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>7.6637922888438696E-10</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>5.3190367443890617E-8</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>2.0262478661578879E-7</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>2.0511439781055759E-7</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>2.2101440611200649E-7</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>1.6317736341870269E-8</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>9.3398958840967376E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>1.3772535565051801E-7</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -4959,7 +4959,7 @@
         <v>2.0369722976204551E-7</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>1.541696770597969E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>2.1658530265339739E-7</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>1.9824109663449151E-8</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>9.3398915281159411E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>1.0796840951073009E-8</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>1.5037177448680371E-8</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>1.706589238254627E-10</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>6.4150873934306188E-11</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>4.307186143247862E-8</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>2.76419553576033E-8</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>5.6050315836556741E-10</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>7.6637922888438696E-10</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>5.3190367443890617E-8</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>2.0262478661578879E-7</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>2.0511439781055759E-7</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>2.2101440611200649E-7</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>1.6317736341870269E-8</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>9.3398958840967376E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>1.3772535565051801E-7</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>2.0369722976204551E-7</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>1.541696770597969E-7</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>2.1658530265339739E-7</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>1.9824109663449151E-8</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>9.3398915281159411E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>1.0796840951073009E-8</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>1.5037177448680371E-8</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>1.706589238254627E-10</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>6.4150873934306188E-11</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>4.307186143247862E-8</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>2.76419553576033E-8</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>5.6050315836556741E-10</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>7.6637922888438696E-10</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>5.3190367443890617E-8</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -7577,7 +7577,7 @@
         <v>2.0262478661578879E-7</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>2.0511439781055759E-7</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>2.2101440611200649E-7</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>1.6317736341870269E-8</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>9.3398958840967376E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>1.3772535565051801E-7</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>2.0369722976204551E-7</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>1.541696770597969E-7</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>2.1658530265339739E-7</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>1.9824109663449151E-8</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -8355,9 +8355,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>1.402876882139269E-10</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>2.3537360539067781E-11</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>7.2616593896916466E-13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>6.0973891777756262E-13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>1.4483715154046109E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>4.7150321839815435E-10</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>1.374944462501474E-12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>1.8584483249450651E-12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>7.331160012784365E-10</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>3.8334046358584866E-9</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>1.7972721579379769E-9</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>4.5611504003834629E-10</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>3.6674314588148632E-11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>1.226376506018906E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -9061,7 +9061,7 @@
         <v>4.162267061827855E-9</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>2.7412580889777388E-9</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>6.2759780469017746E-10</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>4.5103610108137241E-10</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>4.367371891521962E-11</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>1.2263785043172E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>1.402876882139269E-10</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>2.3537360539067781E-11</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>7.2616593896916466E-13</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>6.0973891777756262E-13</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>1.4483715154046109E-9</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>4.7150321839815435E-10</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>1.374944462501474E-12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>1.8584483249450651E-12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>7.331160012784365E-10</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>3.8334046358584866E-9</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>1.7972721579379769E-9</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>4.5611504003834629E-10</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>3.6674314588148632E-11</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -9897,7 +9897,7 @@
         <v>1.226376506018906E-5</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>4.162267061827855E-9</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>2.7412580889777388E-9</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>6.2759780469017746E-10</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>4.5103610108137241E-10</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>4.367371891521962E-11</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>1.2263785043172E-5</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>1.402876882139269E-10</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>2.3537360539067781E-11</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>7.2616593896916466E-13</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>6.0973891777756262E-13</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>1.4483715154046109E-9</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>4.7150321839815435E-10</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>1.374944462501474E-12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>1.8584483249450651E-12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>7.331160012784365E-10</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -10601,7 +10601,7 @@
         <v>3.8334046358584866E-9</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>1.7972721579379769E-9</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>4.5611504003834629E-10</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>3.6674314588148632E-11</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>1.226376506018906E-5</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>4.162267061827855E-9</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>2.7412580889777388E-9</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>6.2759780469017746E-10</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>4.5103610108137241E-10</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -10997,7 +10997,7 @@
         <v>4.367371891521962E-11</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>1.2263785043172E-5</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>1.402876882139269E-10</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -11129,7 +11129,7 @@
         <v>2.3537360539067781E-11</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>7.2616593896916466E-13</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>6.0973891777756262E-13</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>1.4483715154046109E-9</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>4.7150321839815435E-10</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>1.374944462501474E-12</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>1.8584483249450651E-12</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -11437,7 +11437,7 @@
         <v>7.331160012784365E-10</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>3.8334046358584866E-9</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>1.7972721579379769E-9</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>4.5611504003834629E-10</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>3.6674314588148632E-11</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -11657,7 +11657,7 @@
         <v>1.226376506018906E-5</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -11701,7 +11701,7 @@
         <v>4.162267061827855E-9</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -11745,7 +11745,7 @@
         <v>2.7412580889777388E-9</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>6.2759780469017746E-10</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>4.5103610108137241E-10</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>4.367371891521962E-11</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>1.2263785043172E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>1.402876882139269E-10</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>2.3537360539067781E-11</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>7.2616593896916466E-13</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>6.0973891777756262E-13</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -12141,7 +12141,7 @@
         <v>1.4483715154046109E-9</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -12185,7 +12185,7 @@
         <v>4.7150321839815435E-10</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -12229,7 +12229,7 @@
         <v>1.374944462501474E-12</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>1.8584483249450651E-12</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -12317,7 +12317,7 @@
         <v>7.331160012784365E-10</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>3.8334046358584866E-9</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>1.7972721579379769E-9</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -12449,7 +12449,7 @@
         <v>4.5611504003834629E-10</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>3.6674314588148632E-11</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -12537,7 +12537,7 @@
         <v>1.226376506018906E-5</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>4.162267061827855E-9</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -12625,7 +12625,7 @@
         <v>2.7412580889777388E-9</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>6.2759780469017746E-10</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -12713,7 +12713,7 @@
         <v>4.5103610108137241E-10</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -12757,7 +12757,7 @@
         <v>4.367371891521962E-11</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -12809,12 +12809,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12828,7 +12831,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -12842,7 +12845,7 @@
         <v>0.97167031836320727</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -12856,7 +12859,7 @@
         <v>0.49644292870392021</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -12870,7 +12873,7 @@
         <v>3.459980561540859E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -12884,7 +12887,7 @@
         <v>1.1672522258796369E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -12898,7 +12901,7 @@
         <v>0.98327466366265093</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -12912,7 +12915,7 @@
         <v>0.63623445139225043</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -12926,7 +12929,7 @@
         <v>0.1088017696921048</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -12940,7 +12943,7 @@
         <v>0.14848143489933999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -12954,7 +12957,7 @@
         <v>4.3204980737387171</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -12968,7 +12971,7 @@
         <v>4.6099572210147448</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -12982,7 +12985,7 @@
         <v>5.1521373860921171</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -12996,7 +12999,7 @@
         <v>10.394992016715021</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -13010,7 +13013,7 @@
         <v>3.7250373918088688</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -13024,7 +13027,7 @@
         <v>49.126164751765323</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -13038,7 +13041,7 @@
         <v>5.3947712349145611</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -13052,7 +13055,7 @@
         <v>15.60301276143889</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -13066,7 +13069,7 @@
         <v>15.929338171658451</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -13080,7 +13083,7 @@
         <v>11.12291931912913</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -13094,7 +13097,7 @@
         <v>6.1247289567723584</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -13108,7 +13111,7 @@
         <v>49.847866396170907</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -13122,7 +13125,7 @@
         <v>0.95853164076923436</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -13136,7 +13139,7 @@
         <v>0.50044849607854625</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -13150,7 +13153,7 @@
         <v>3.4790589935715301E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -13164,7 +13167,7 @@
         <v>1.172064959172201E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -13178,7 +13181,7 @@
         <v>0.96646219204724726</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -13192,7 +13195,7 @@
         <v>0.63772813833662512</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -13206,7 +13209,7 @@
         <v>0.12755567757005051</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -13220,7 +13223,7 @@
         <v>0.14771957821773199</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -13234,7 +13237,7 @@
         <v>4.266656756455566</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -13248,7 +13251,7 @@
         <v>4.6157530127901287</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -13262,7 +13265,7 @@
         <v>5.0197176478844456</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -13276,7 +13279,7 @@
         <v>10.298786255796029</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>3.6069853102768219</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -13304,7 +13307,7 @@
         <v>48.388135031278502</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -13318,7 +13321,7 @@
         <v>5.2443370114256567</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -13332,7 +13335,7 @@
         <v>15.569434523668029</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -13346,7 +13349,7 @@
         <v>15.24705995297068</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -13360,7 +13363,7 @@
         <v>10.96898027532105</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -13374,7 +13377,7 @@
         <v>5.7444008907244406</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -13388,7 +13391,7 @@
         <v>49.035825056429879</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -13402,7 +13405,7 @@
         <v>0.87023167628512144</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -13416,7 +13419,7 @@
         <v>0.49621092020447921</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -13430,7 +13433,7 @@
         <v>3.439296018600374E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -13444,7 +13447,7 @@
         <v>1.1304986376785011E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -13458,7 +13461,7 @@
         <v>0.90100416616041967</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -13472,7 +13475,7 @@
         <v>0.62829687186290761</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -13486,7 +13489,7 @@
         <v>0.13120772779156259</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -13500,7 +13503,7 @@
         <v>0.1438067717221983</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -13514,7 +13517,7 @@
         <v>4.0089528612702141</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -13528,7 +13531,7 @@
         <v>4.4922818194578102</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -13542,7 +13545,7 @@
         <v>4.5747437756904539</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -13556,7 +13559,7 @@
         <v>9.9866581664967171</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -13570,7 +13573,7 @@
         <v>3.3142560258713951</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -13584,7 +13587,7 @@
         <v>46.558863261026552</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -13598,7 +13601,7 @@
         <v>4.8003065021548323</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -13612,7 +13615,7 @@
         <v>15.395464165356319</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -13626,7 +13629,7 @@
         <v>13.93985458175962</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -13640,7 +13643,7 @@
         <v>10.62401839138564</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -13654,7 +13657,7 @@
         <v>5.3665488738997356</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -13668,7 +13671,7 @@
         <v>47.199619710848879</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -13682,7 +13685,7 @@
         <v>0.76276052222521995</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -13696,7 +13699,7 @@
         <v>0.48552449201578901</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -13710,7 +13713,7 @@
         <v>3.3966841855206181E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>1.079375982954524E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -13738,7 +13741,7 @@
         <v>0.82770691470285429</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -13752,7 +13755,7 @@
         <v>0.6076006208463347</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -13766,7 +13769,7 @@
         <v>0.123917574057962</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -13780,7 +13783,7 @@
         <v>0.13404910041173021</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -13794,7 +13797,7 @@
         <v>3.6977278232095641</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -13808,7 +13811,7 @@
         <v>4.279127239183957</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -13822,7 +13825,7 @@
         <v>4.0883818959987748</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -13836,7 +13839,7 @@
         <v>9.6426611136666249</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -13850,7 +13853,7 @@
         <v>2.9378558977901119</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -13864,7 +13867,7 @@
         <v>44.853041101783553</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -13878,7 +13881,7 @@
         <v>4.3504571775812861</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -13892,7 +13895,7 @@
         <v>15.18774220149121</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -13906,7 +13909,7 @@
         <v>12.684425186813289</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -13920,7 +13923,7 @@
         <v>10.2521460364571</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -13934,7 +13937,7 @@
         <v>4.9027168479598791</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -13948,7 +13951,7 @@
         <v>45.46430141683701</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -13962,7 +13965,7 @@
         <v>0.65439716101086054</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -13976,7 +13979,7 @@
         <v>0.45672104436987893</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -13990,7 +13993,7 @@
         <v>3.2950707005107348E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -14004,7 +14007,7 @@
         <v>1.026663845042974E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -14018,7 +14021,7 @@
         <v>0.71240786065995632</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -14032,7 +14035,7 @@
         <v>0.55989132462612246</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -14046,7 +14049,7 @@
         <v>0.11189693634869741</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -14060,7 +14063,7 @@
         <v>0.11767796271468969</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -14074,7 +14077,7 @@
         <v>3.2911374316298998</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -14088,7 +14091,7 @@
         <v>3.9090630444153649</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -14102,7 +14105,7 @@
         <v>3.4786171848259322</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -14116,7 +14119,7 @@
         <v>8.9920675777664538</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -14130,7 +14133,7 @@
         <v>2.495493948522332</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -14144,7 +14147,7 @@
         <v>41.180452073478392</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -14158,7 +14161,7 @@
         <v>3.541518681748121</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -14172,7 +14175,7 @@
         <v>14.67126312235008</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -14186,7 +14189,7 @@
         <v>10.62427925978908</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -14200,7 +14203,7 @@
         <v>9.4117762544718744</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -14214,7 +14217,7 @@
         <v>3.6796432285710581</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>25</v>
       </c>
